--- a/data/nzd0416/nzd0416.xlsx
+++ b/data/nzd0416/nzd0416.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K747"/>
+  <dimension ref="A1:K753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29537,6 +29537,240 @@
         <v>312.52</v>
       </c>
       <c r="K747" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>309.2</v>
+      </c>
+      <c r="C748" t="n">
+        <v>299.15</v>
+      </c>
+      <c r="D748" t="n">
+        <v>292.47</v>
+      </c>
+      <c r="E748" t="n">
+        <v>301.44</v>
+      </c>
+      <c r="F748" t="n">
+        <v>296.83</v>
+      </c>
+      <c r="G748" t="n">
+        <v>311.88</v>
+      </c>
+      <c r="H748" t="n">
+        <v>309.59</v>
+      </c>
+      <c r="I748" t="n">
+        <v>307.65</v>
+      </c>
+      <c r="J748" t="n">
+        <v>308.25</v>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:07:01+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>308.82</v>
+      </c>
+      <c r="C749" t="n">
+        <v>298.24</v>
+      </c>
+      <c r="D749" t="n">
+        <v>291.36</v>
+      </c>
+      <c r="E749" t="n">
+        <v>300.36</v>
+      </c>
+      <c r="F749" t="n">
+        <v>295.18</v>
+      </c>
+      <c r="G749" t="n">
+        <v>310.81</v>
+      </c>
+      <c r="H749" t="n">
+        <v>308.83</v>
+      </c>
+      <c r="I749" t="n">
+        <v>307.65</v>
+      </c>
+      <c r="J749" t="n">
+        <v>308.25</v>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:13+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>305.92</v>
+      </c>
+      <c r="C750" t="n">
+        <v>293.46</v>
+      </c>
+      <c r="D750" t="n">
+        <v>285.54</v>
+      </c>
+      <c r="E750" t="n">
+        <v>294.55</v>
+      </c>
+      <c r="F750" t="n">
+        <v>288.01</v>
+      </c>
+      <c r="G750" t="n">
+        <v>305.67</v>
+      </c>
+      <c r="H750" t="n">
+        <v>303.52</v>
+      </c>
+      <c r="I750" t="n">
+        <v>302.44</v>
+      </c>
+      <c r="J750" t="n">
+        <v>302</v>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>305.92</v>
+      </c>
+      <c r="C751" t="n">
+        <v>293.46</v>
+      </c>
+      <c r="D751" t="n">
+        <v>283.64</v>
+      </c>
+      <c r="E751" t="n">
+        <v>292.65</v>
+      </c>
+      <c r="F751" t="n">
+        <v>285.73</v>
+      </c>
+      <c r="G751" t="n">
+        <v>305.67</v>
+      </c>
+      <c r="H751" t="n">
+        <v>301.92</v>
+      </c>
+      <c r="I751" t="n">
+        <v>300.73</v>
+      </c>
+      <c r="J751" t="n">
+        <v>299.82</v>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>306.06</v>
+      </c>
+      <c r="C752" t="n">
+        <v>293.33</v>
+      </c>
+      <c r="D752" t="n">
+        <v>283.2</v>
+      </c>
+      <c r="E752" t="n">
+        <v>292.21</v>
+      </c>
+      <c r="F752" t="n">
+        <v>284.98</v>
+      </c>
+      <c r="G752" t="n">
+        <v>304.75</v>
+      </c>
+      <c r="H752" t="n">
+        <v>301.66</v>
+      </c>
+      <c r="I752" t="n">
+        <v>300.46</v>
+      </c>
+      <c r="J752" t="n">
+        <v>299.73</v>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>303.81</v>
+      </c>
+      <c r="C753" t="n">
+        <v>291.45</v>
+      </c>
+      <c r="D753" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="E753" t="n">
+        <v>288.56</v>
+      </c>
+      <c r="F753" t="n">
+        <v>280.53</v>
+      </c>
+      <c r="G753" t="n">
+        <v>302.84</v>
+      </c>
+      <c r="H753" t="n">
+        <v>298.43</v>
+      </c>
+      <c r="I753" t="n">
+        <v>297.28</v>
+      </c>
+      <c r="J753" t="n">
+        <v>295.67</v>
+      </c>
+      <c r="K753" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29553,7 +29787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B839"/>
+  <dimension ref="A1:B845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37946,6 +38180,66 @@
       </c>
       <c r="B839" t="n">
         <v>-0.14</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B840" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B841" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B842" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B843" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B844" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B845" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -38114,28 +38408,28 @@
         <v>0.0689</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6009675940440363</v>
+        <v>-0.6139811966121596</v>
       </c>
       <c r="J2" t="n">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="K2" t="n">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08169360326150255</v>
+        <v>0.08611310839671338</v>
       </c>
       <c r="M2" t="n">
-        <v>13.17186801824132</v>
+        <v>13.12901329333503</v>
       </c>
       <c r="N2" t="n">
-        <v>239.2814003120154</v>
+        <v>237.9790186805189</v>
       </c>
       <c r="O2" t="n">
-        <v>15.46872329289057</v>
+        <v>15.42656859708337</v>
       </c>
       <c r="P2" t="n">
-        <v>331.4079639855224</v>
+        <v>331.5426803548841</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38192,28 +38486,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7767137186594443</v>
+        <v>-0.8040210698888968</v>
       </c>
       <c r="J3" t="n">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="K3" t="n">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07565492413900443</v>
+        <v>0.08146326711201879</v>
       </c>
       <c r="M3" t="n">
-        <v>17.2377201657137</v>
+        <v>17.23987073175349</v>
       </c>
       <c r="N3" t="n">
-        <v>434.4363530887795</v>
+        <v>433.5856600508951</v>
       </c>
       <c r="O3" t="n">
-        <v>20.84313683419028</v>
+        <v>20.82271980436022</v>
       </c>
       <c r="P3" t="n">
-        <v>333.8393502886429</v>
+        <v>334.1220166155827</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38270,28 +38564,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5798110981129037</v>
+        <v>-0.611474427064079</v>
       </c>
       <c r="J4" t="n">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="K4" t="n">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02241434662531683</v>
+        <v>0.02518622032173534</v>
       </c>
       <c r="M4" t="n">
-        <v>25.36632837891356</v>
+        <v>25.32941508275076</v>
       </c>
       <c r="N4" t="n">
-        <v>857.0164224219209</v>
+        <v>853.7095687284501</v>
       </c>
       <c r="O4" t="n">
-        <v>29.27484282488842</v>
+        <v>29.21830879309153</v>
       </c>
       <c r="P4" t="n">
-        <v>322.3932352560744</v>
+        <v>322.7232735276039</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38348,28 +38642,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.634580632827028</v>
+        <v>-0.6599099864982926</v>
       </c>
       <c r="J5" t="n">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="K5" t="n">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03624657223714045</v>
+        <v>0.03959367716598094</v>
       </c>
       <c r="M5" t="n">
-        <v>21.69784541898483</v>
+        <v>21.65966939502073</v>
       </c>
       <c r="N5" t="n">
-        <v>625.7980279488012</v>
+        <v>623.1263640810761</v>
       </c>
       <c r="O5" t="n">
-        <v>25.0159554674372</v>
+        <v>24.96249915535454</v>
       </c>
       <c r="P5" t="n">
-        <v>328.6932195882901</v>
+        <v>328.9571210204411</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38426,28 +38720,28 @@
         <v>0.0738</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6369437704957794</v>
+        <v>-0.6644996948666666</v>
       </c>
       <c r="J6" t="n">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="K6" t="n">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03291367703259196</v>
+        <v>0.03617646739898173</v>
       </c>
       <c r="M6" t="n">
-        <v>22.96102518232948</v>
+        <v>22.9236470040536</v>
       </c>
       <c r="N6" t="n">
-        <v>696.7108870893813</v>
+        <v>693.9664798366041</v>
       </c>
       <c r="O6" t="n">
-        <v>26.39528153078465</v>
+        <v>26.34324353295554</v>
       </c>
       <c r="P6" t="n">
-        <v>323.8037352272059</v>
+        <v>324.0908473108795</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38504,28 +38798,28 @@
         <v>0.07820000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5006570874595987</v>
+        <v>-0.5199752019080013</v>
       </c>
       <c r="J7" t="n">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="K7" t="n">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04149196145509537</v>
+        <v>0.04517935168015097</v>
       </c>
       <c r="M7" t="n">
-        <v>15.84679142574594</v>
+        <v>15.8269079803777</v>
       </c>
       <c r="N7" t="n">
-        <v>338.4340888069993</v>
+        <v>337.0735106598552</v>
       </c>
       <c r="O7" t="n">
-        <v>18.39657818201524</v>
+        <v>18.35956183191351</v>
       </c>
       <c r="P7" t="n">
-        <v>333.1130382122285</v>
+        <v>333.3143049675267</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38582,28 +38876,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3969869318691774</v>
+        <v>-0.4171617205277933</v>
       </c>
       <c r="J8" t="n">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="K8" t="n">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02147869021371707</v>
+        <v>0.02398230545195579</v>
       </c>
       <c r="M8" t="n">
-        <v>17.66540635289727</v>
+        <v>17.63146542920591</v>
       </c>
       <c r="N8" t="n">
-        <v>419.6396203035999</v>
+        <v>417.7853560016529</v>
       </c>
       <c r="O8" t="n">
-        <v>20.48510728074422</v>
+        <v>20.43979833564052</v>
       </c>
       <c r="P8" t="n">
-        <v>327.942552829613</v>
+        <v>328.1527553308903</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38660,28 +38954,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3434591335696336</v>
+        <v>-0.365616421073604</v>
       </c>
       <c r="J9" t="n">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="K9" t="n">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01439058682182293</v>
+        <v>0.01649351564680779</v>
       </c>
       <c r="M9" t="n">
-        <v>18.71483020099853</v>
+        <v>18.68575200824945</v>
       </c>
       <c r="N9" t="n">
-        <v>472.2131193199422</v>
+        <v>470.2111565290014</v>
       </c>
       <c r="O9" t="n">
-        <v>21.73046523477908</v>
+        <v>21.68435280401519</v>
       </c>
       <c r="P9" t="n">
-        <v>326.5232193734881</v>
+        <v>326.7540689789905</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38738,28 +39032,28 @@
         <v>0.0471</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3585962607474918</v>
+        <v>-0.3813761772398452</v>
       </c>
       <c r="J10" t="n">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="K10" t="n">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01071127118929727</v>
+        <v>0.01227117862884475</v>
       </c>
       <c r="M10" t="n">
-        <v>22.82343692142227</v>
+        <v>22.76395191708715</v>
       </c>
       <c r="N10" t="n">
-        <v>705.7762666849524</v>
+        <v>702.0585537546842</v>
       </c>
       <c r="O10" t="n">
-        <v>26.56645002037255</v>
+        <v>26.49638756047104</v>
       </c>
       <c r="P10" t="n">
-        <v>327.0470682165046</v>
+        <v>327.282233567078</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38797,7 +39091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K747"/>
+  <dimension ref="A1:K753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81299,6 +81593,348 @@
         </is>
       </c>
     </row>
+    <row r="748">
+      <c r="A748" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>-43.04859276530645,173.07191878013217</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>-43.04837193311405,173.07106366636094</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>-43.048177850866615,173.07017826951085</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>-43.04816552728801,173.0692276784811</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>-43.04809816594012,173.06830160952714</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>-43.04821764365314,173.06738070633733</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>-43.048228179378235,173.0664671680656</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>-43.04824155560589,173.06556871030654</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>-43.048277778684486,173.06467173519044</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:07:01+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>-43.04858941324508,173.07191971799068</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>-43.04836390581995,173.07106591235106</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>-43.048167996644835,173.07018055334223</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>-43.04815583741811,173.06922881113206</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>-43.048083314499564,173.06830222364192</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>-43.04820800898063,173.0673805491769</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>-43.04822134330907,173.06646672440846</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>-43.04824155560589,173.06556871030654</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>-43.048277778684486,173.06467173519044</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:13+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>-43.04856383172385,173.07192687532844</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>-43.048321740471955,173.07107770995984</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>-43.04811632856202,173.0701925280137</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>-43.04810370950648,173.0692349043687</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>-43.048018778239204,173.06830489224643</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>-43.04816172653489,173.06737979422007</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>-43.04817358077292,173.06646362464886</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>-43.048194692536185,173.06556566938195</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>-43.04822156097103,173.06466808779777</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>-43.04856383172385,173.07192687532844</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>-43.048321740471955,173.07107770995984</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>-43.048099460974484,173.0701964372664</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>-43.048086662512844,173.0692368969912</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>-43.04799825624832,173.06830574083918</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>-43.04816172653489,173.06737979422007</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>-43.04815918904818,173.06646269063563</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>-43.048179311375016,173.06556467130596</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>-43.048201952232404,173.06466681558877</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>-43.04856506669385,173.07192652980194</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>-43.048320593715616,173.07107803081507</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>-43.04809555479628,173.0701973425667</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>-43.04808271478798,173.06923735844046</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>-43.04799150559339,173.0683060199814</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>-43.04815344251733,173.06737965909173</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>-43.04815685039291,173.0664625388585</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>-43.048176882770605,173.0655645137151</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>-43.04820114269733,173.06466676306638</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>-43.04854521896148,173.07193208290497</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>-43.04830400985446,173.0710826708742</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>-43.04806350637937,173.07020477013992</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>-43.0480499666157,173.06924118636957</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>-43.04795145170735,173.06830767622407</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>-43.04813624417648,173.06737937855368</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>-43.04812779709844,173.06646065332075</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>-43.04814827920756,173.06556265764547</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>-43.04816462367014,173.0646643937253</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0416/nzd0416.xlsx
+++ b/data/nzd0416/nzd0416.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K753"/>
+  <dimension ref="A1:K758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29771,6 +29771,201 @@
         <v>295.67</v>
       </c>
       <c r="K753" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>304.28</v>
+      </c>
+      <c r="C754" t="n">
+        <v>291.45</v>
+      </c>
+      <c r="D754" t="n">
+        <v>275.93</v>
+      </c>
+      <c r="E754" t="n">
+        <v>285.53</v>
+      </c>
+      <c r="F754" t="n">
+        <v>276.76</v>
+      </c>
+      <c r="G754" t="n">
+        <v>299.84</v>
+      </c>
+      <c r="H754" t="n">
+        <v>295.74</v>
+      </c>
+      <c r="I754" t="n">
+        <v>294.77</v>
+      </c>
+      <c r="J754" t="n">
+        <v>292.12</v>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:13:29+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>303.63</v>
+      </c>
+      <c r="C755" t="n">
+        <v>290.54</v>
+      </c>
+      <c r="D755" t="n">
+        <v>274.79</v>
+      </c>
+      <c r="E755" t="n">
+        <v>284.29</v>
+      </c>
+      <c r="F755" t="n">
+        <v>275.36</v>
+      </c>
+      <c r="G755" t="n">
+        <v>298.45</v>
+      </c>
+      <c r="H755" t="n">
+        <v>294.76</v>
+      </c>
+      <c r="I755" t="n">
+        <v>293.58</v>
+      </c>
+      <c r="J755" t="n">
+        <v>290.48</v>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>302.8</v>
+      </c>
+      <c r="C756" t="n">
+        <v>289.37</v>
+      </c>
+      <c r="D756" t="n">
+        <v>273.65</v>
+      </c>
+      <c r="E756" t="n">
+        <v>283.18</v>
+      </c>
+      <c r="F756" t="n">
+        <v>274.1</v>
+      </c>
+      <c r="G756" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="H756" t="n">
+        <v>293.7</v>
+      </c>
+      <c r="I756" t="n">
+        <v>292.69</v>
+      </c>
+      <c r="J756" t="n">
+        <v>289.1</v>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:36+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>303.02</v>
+      </c>
+      <c r="C757" t="n">
+        <v>288.81</v>
+      </c>
+      <c r="D757" t="n">
+        <v>271.42</v>
+      </c>
+      <c r="E757" t="n">
+        <v>281.19</v>
+      </c>
+      <c r="F757" t="n">
+        <v>271.98</v>
+      </c>
+      <c r="G757" t="n">
+        <v>295.87</v>
+      </c>
+      <c r="H757" t="n">
+        <v>292.18</v>
+      </c>
+      <c r="I757" t="n">
+        <v>290.74</v>
+      </c>
+      <c r="J757" t="n">
+        <v>287.02</v>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>302.84</v>
+      </c>
+      <c r="C758" t="n">
+        <v>288.65</v>
+      </c>
+      <c r="D758" t="n">
+        <v>270.9</v>
+      </c>
+      <c r="E758" t="n">
+        <v>280.74</v>
+      </c>
+      <c r="F758" t="n">
+        <v>271.7</v>
+      </c>
+      <c r="G758" t="n">
+        <v>295.6</v>
+      </c>
+      <c r="H758" t="n">
+        <v>291.86</v>
+      </c>
+      <c r="I758" t="n">
+        <v>290.37</v>
+      </c>
+      <c r="J758" t="n">
+        <v>286.36</v>
+      </c>
+      <c r="K758" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29787,7 +29982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B845"/>
+  <dimension ref="A1:B850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38240,6 +38435,56 @@
       </c>
       <c r="B845" t="n">
         <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B846" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B847" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B848" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B849" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B850" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -38408,28 +38653,28 @@
         <v>0.0689</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6139811966121596</v>
+        <v>-0.6284515296038992</v>
       </c>
       <c r="J2" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K2" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08611310839671338</v>
+        <v>0.09070705656122646</v>
       </c>
       <c r="M2" t="n">
-        <v>13.12901329333503</v>
+        <v>13.11243643520737</v>
       </c>
       <c r="N2" t="n">
-        <v>237.9790186805189</v>
+        <v>237.2897274726174</v>
       </c>
       <c r="O2" t="n">
-        <v>15.42656859708337</v>
+        <v>15.40421135510083</v>
       </c>
       <c r="P2" t="n">
-        <v>331.5426803548841</v>
+        <v>331.693079303439</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38486,28 +38731,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8040210698888968</v>
+        <v>-0.8321417635893301</v>
       </c>
       <c r="J3" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K3" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08146326711201879</v>
+        <v>0.08727008298397076</v>
       </c>
       <c r="M3" t="n">
-        <v>17.23987073175349</v>
+        <v>17.26966224410131</v>
       </c>
       <c r="N3" t="n">
-        <v>433.5856600508951</v>
+        <v>434.0543877432959</v>
       </c>
       <c r="O3" t="n">
-        <v>20.82271980436022</v>
+        <v>20.83397196271743</v>
       </c>
       <c r="P3" t="n">
-        <v>334.1220166155827</v>
+        <v>334.414293512483</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38564,28 +38809,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.611474427064079</v>
+        <v>-0.6525865434780396</v>
       </c>
       <c r="J4" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K4" t="n">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02518622032173534</v>
+        <v>0.02875146573761866</v>
       </c>
       <c r="M4" t="n">
-        <v>25.32941508275076</v>
+        <v>25.37594989094831</v>
       </c>
       <c r="N4" t="n">
-        <v>853.7095687284501</v>
+        <v>855.0989341169228</v>
       </c>
       <c r="O4" t="n">
-        <v>29.21830879309153</v>
+        <v>29.24207472319505</v>
       </c>
       <c r="P4" t="n">
-        <v>322.7232735276039</v>
+        <v>323.1535180382097</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38642,28 +38887,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6599099864982926</v>
+        <v>-0.6951106155066685</v>
       </c>
       <c r="J5" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K5" t="n">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03959367716598094</v>
+        <v>0.04398741247867788</v>
       </c>
       <c r="M5" t="n">
-        <v>21.65966939502073</v>
+        <v>21.70384427900117</v>
       </c>
       <c r="N5" t="n">
-        <v>623.1263640810761</v>
+        <v>624.1692553767327</v>
       </c>
       <c r="O5" t="n">
-        <v>24.96249915535454</v>
+        <v>24.98337958276928</v>
       </c>
       <c r="P5" t="n">
-        <v>328.9571210204411</v>
+        <v>329.3253195484943</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38720,28 +38965,28 @@
         <v>0.0738</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6644996948666666</v>
+        <v>-0.704714016943362</v>
       </c>
       <c r="J6" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K6" t="n">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03617646739898173</v>
+        <v>0.04067883746497891</v>
       </c>
       <c r="M6" t="n">
-        <v>22.9236470040536</v>
+        <v>22.9850686044978</v>
       </c>
       <c r="N6" t="n">
-        <v>693.9664798366041</v>
+        <v>696.1144481701674</v>
       </c>
       <c r="O6" t="n">
-        <v>26.34324353295554</v>
+        <v>26.38398090073155</v>
       </c>
       <c r="P6" t="n">
-        <v>324.0908473108795</v>
+        <v>324.5114871341431</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38798,28 +39043,28 @@
         <v>0.07820000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5199752019080013</v>
+        <v>-0.5472606729026391</v>
       </c>
       <c r="J7" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K7" t="n">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04517935168015097</v>
+        <v>0.0500380669076026</v>
       </c>
       <c r="M7" t="n">
-        <v>15.8269079803777</v>
+        <v>15.87158544957956</v>
       </c>
       <c r="N7" t="n">
-        <v>337.0735106598552</v>
+        <v>337.9508129134396</v>
       </c>
       <c r="O7" t="n">
-        <v>18.35956183191351</v>
+        <v>18.38343854977734</v>
       </c>
       <c r="P7" t="n">
-        <v>333.3143049675267</v>
+        <v>333.5997130128019</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38876,28 +39121,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4171617205277933</v>
+        <v>-0.4462139713396626</v>
       </c>
       <c r="J8" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K8" t="n">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02398230545195579</v>
+        <v>0.02749790315380751</v>
       </c>
       <c r="M8" t="n">
-        <v>17.63146542920591</v>
+        <v>17.66819021764264</v>
       </c>
       <c r="N8" t="n">
-        <v>417.7853560016529</v>
+        <v>418.5396752938715</v>
       </c>
       <c r="O8" t="n">
-        <v>20.43979833564052</v>
+        <v>20.4582422337275</v>
       </c>
       <c r="P8" t="n">
-        <v>328.1527553308903</v>
+        <v>328.4566414810795</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38954,28 +39199,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.365616421073604</v>
+        <v>-0.3961819313118646</v>
       </c>
       <c r="J9" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K9" t="n">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01649351564680779</v>
+        <v>0.01942281847200489</v>
       </c>
       <c r="M9" t="n">
-        <v>18.68575200824945</v>
+        <v>18.72621114716035</v>
       </c>
       <c r="N9" t="n">
-        <v>470.2111565290014</v>
+        <v>470.9970610958311</v>
       </c>
       <c r="O9" t="n">
-        <v>21.68435280401519</v>
+        <v>21.70246670532709</v>
       </c>
       <c r="P9" t="n">
-        <v>326.7540689789905</v>
+        <v>327.0737854780817</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39032,28 +39277,28 @@
         <v>0.0471</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3813761772398452</v>
+        <v>-0.4160497586002321</v>
       </c>
       <c r="J10" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K10" t="n">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01227117862884475</v>
+        <v>0.0146672801633132</v>
       </c>
       <c r="M10" t="n">
-        <v>22.76395191708715</v>
+        <v>22.800437628039</v>
       </c>
       <c r="N10" t="n">
-        <v>702.0585537546842</v>
+        <v>702.5203980863041</v>
       </c>
       <c r="O10" t="n">
-        <v>26.49638756047104</v>
+        <v>26.50510135966856</v>
       </c>
       <c r="P10" t="n">
-        <v>327.282233567078</v>
+        <v>327.6416222661748</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39091,7 +39336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K753"/>
+  <dimension ref="A1:K758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81935,6 +82180,291 @@
         </is>
       </c>
     </row>
+    <row r="754">
+      <c r="A754" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>-43.04854936493227,173.07193092292377</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>-43.04830400985446,173.0710826708742</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>-43.0480310140779,173.07021230058027</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>-43.04802278114642,173.06924436407203</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>-43.04791751841489,173.0683090793763</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>-43.04810923107556,173.0673789379183</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>-43.048103601010965,173.06645908301363</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>-43.04812570218127,173.0655611926358</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>-43.04813269200821,173.0646623220131</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:13:29+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>-43.048543631142884,173.07193252715308</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>-43.0482959825599,173.07108491685938</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>-43.04802089352484,173.07021464612563</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>-43.04801165573978,173.06924566451713</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>-43.04790491719218,173.0683096004404</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>-43.04809671500543,173.0673787337574</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>-43.04809478607944,173.06645851093177</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>-43.04811499833211,173.06556049806986</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>-43.0481179404798,173.06466136494117</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>-43.048536309534846,173.07193457563008</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>-43.048285661752494,173.0710878045537</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>-43.04801077297172,173.07021699167024</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>-43.04800169670639,173.0692468286248</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>-43.04789357609171,173.0683100693979</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>-43.04808816085675,173.06737859422302</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>-43.048085251561645,173.06645789214954</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>-43.048106992932304,173.0655599786047</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>-43.04810552760831,173.06466055960053</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:36+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>-43.04853825020203,173.07193403266032</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>-43.04828072187885,173.07108918669766</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>-43.04799097574921,173.07022157988249</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>-43.04798384222305,173.06924891562778</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>-43.04787449424006,173.06831085843714</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>-43.04807348373848,173.06737835481147</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>-43.04807157942289,173.06645700483952</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>-43.04808945301132,173.06555884045125</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>-43.04808681835266,173.06465934575436</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>-43.048536662383434,173.0719344769083</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>-43.048279310486365,173.0710895815959</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>-43.047986359356464,173.07022264977905</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>-43.047979804777036,173.06924938756296</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>-43.0478719739955,173.0683109626498</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>-43.04807105255937,173.06737831515434</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>-43.04806870107787,173.06645681803747</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>-43.048086124923735,173.065558624494</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>-43.0480808817619,173.06465896059177</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0416/nzd0416.xlsx
+++ b/data/nzd0416/nzd0416.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K758"/>
+  <dimension ref="A1:K760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29966,6 +29966,84 @@
         <v>286.36</v>
       </c>
       <c r="K758" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:40+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>301.7</v>
+      </c>
+      <c r="C759" t="n">
+        <v>285.75</v>
+      </c>
+      <c r="D759" t="n">
+        <v>264.1</v>
+      </c>
+      <c r="E759" t="n">
+        <v>276.21</v>
+      </c>
+      <c r="F759" t="n">
+        <v>266.08</v>
+      </c>
+      <c r="G759" t="n">
+        <v>291.24</v>
+      </c>
+      <c r="H759" t="n">
+        <v>287.3</v>
+      </c>
+      <c r="I759" t="n">
+        <v>285.49</v>
+      </c>
+      <c r="J759" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>302.25</v>
+      </c>
+      <c r="C760" t="n">
+        <v>286.84</v>
+      </c>
+      <c r="D760" t="n">
+        <v>264.1</v>
+      </c>
+      <c r="E760" t="n">
+        <v>278.25</v>
+      </c>
+      <c r="F760" t="n">
+        <v>268.81</v>
+      </c>
+      <c r="G760" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="H760" t="n">
+        <v>288.23</v>
+      </c>
+      <c r="I760" t="n">
+        <v>286.52</v>
+      </c>
+      <c r="J760" t="n">
+        <v>280.47</v>
+      </c>
+      <c r="K760" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29982,7 +30060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B850"/>
+  <dimension ref="A1:B852"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38485,6 +38563,26 @@
       </c>
       <c r="B850" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B851" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B852" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -38653,28 +38751,28 @@
         <v>0.0689</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6284515296038992</v>
+        <v>-0.634752880072639</v>
       </c>
       <c r="J2" t="n">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="K2" t="n">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09070705656122646</v>
+        <v>0.09268916772811575</v>
       </c>
       <c r="M2" t="n">
-        <v>13.11243643520737</v>
+        <v>13.10869325218298</v>
       </c>
       <c r="N2" t="n">
-        <v>237.2897274726174</v>
+        <v>237.0874018595972</v>
       </c>
       <c r="O2" t="n">
-        <v>15.40421135510083</v>
+        <v>15.39764273710743</v>
       </c>
       <c r="P2" t="n">
-        <v>331.693079303439</v>
+        <v>331.7588032521239</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38731,28 +38829,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8321417635893301</v>
+        <v>-0.844829449090616</v>
       </c>
       <c r="J3" t="n">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="K3" t="n">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08727008298397076</v>
+        <v>0.08984812223311001</v>
       </c>
       <c r="M3" t="n">
-        <v>17.26966224410131</v>
+        <v>17.28981700666517</v>
       </c>
       <c r="N3" t="n">
-        <v>434.0543877432959</v>
+        <v>434.6252530232867</v>
       </c>
       <c r="O3" t="n">
-        <v>20.83397196271743</v>
+        <v>20.84766780777377</v>
       </c>
       <c r="P3" t="n">
-        <v>334.414293512483</v>
+        <v>334.5466278159421</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38809,28 +38907,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6525865434780396</v>
+        <v>-0.6732574890466492</v>
       </c>
       <c r="J4" t="n">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="K4" t="n">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02875146573761866</v>
+        <v>0.0305567210040748</v>
       </c>
       <c r="M4" t="n">
-        <v>25.37594989094831</v>
+        <v>25.41672340509596</v>
       </c>
       <c r="N4" t="n">
-        <v>855.0989341169228</v>
+        <v>857.3343188323732</v>
       </c>
       <c r="O4" t="n">
-        <v>29.24207472319505</v>
+        <v>29.28027183672264</v>
       </c>
       <c r="P4" t="n">
-        <v>323.1535180382097</v>
+        <v>323.37059449185</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38887,28 +38985,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6951106155066685</v>
+        <v>-0.7117230509810634</v>
       </c>
       <c r="J5" t="n">
+        <v>759</v>
+      </c>
+      <c r="K5" t="n">
         <v>757</v>
       </c>
-      <c r="K5" t="n">
-        <v>755</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.04398741247867788</v>
+        <v>0.04606076152432892</v>
       </c>
       <c r="M5" t="n">
-        <v>21.70384427900117</v>
+        <v>21.73449487161596</v>
       </c>
       <c r="N5" t="n">
-        <v>624.1692553767327</v>
+        <v>625.4263185545759</v>
       </c>
       <c r="O5" t="n">
-        <v>24.98337958276928</v>
+        <v>25.00852491760712</v>
       </c>
       <c r="P5" t="n">
-        <v>329.3253195484943</v>
+        <v>329.499687514878</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38965,28 +39063,28 @@
         <v>0.0738</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.704714016943362</v>
+        <v>-0.7236816996466225</v>
       </c>
       <c r="J6" t="n">
+        <v>759</v>
+      </c>
+      <c r="K6" t="n">
         <v>757</v>
       </c>
-      <c r="K6" t="n">
-        <v>755</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.04067883746497891</v>
+        <v>0.04281156582999246</v>
       </c>
       <c r="M6" t="n">
-        <v>22.9850686044978</v>
+        <v>23.02409299142698</v>
       </c>
       <c r="N6" t="n">
-        <v>696.1144481701674</v>
+        <v>698.0652204756543</v>
       </c>
       <c r="O6" t="n">
-        <v>26.38398090073155</v>
+        <v>26.42092391411879</v>
       </c>
       <c r="P6" t="n">
-        <v>324.5114871341431</v>
+        <v>324.710576256429</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39043,28 +39141,28 @@
         <v>0.07820000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5472606729026391</v>
+        <v>-0.5606225283244582</v>
       </c>
       <c r="J7" t="n">
+        <v>759</v>
+      </c>
+      <c r="K7" t="n">
         <v>757</v>
       </c>
-      <c r="K7" t="n">
-        <v>755</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0500380669076026</v>
+        <v>0.05238619635201003</v>
       </c>
       <c r="M7" t="n">
-        <v>15.87158544957956</v>
+        <v>15.90216961159383</v>
       </c>
       <c r="N7" t="n">
-        <v>337.9508129134396</v>
+        <v>338.9378680542418</v>
       </c>
       <c r="O7" t="n">
-        <v>18.38343854977734</v>
+        <v>18.41026529016466</v>
       </c>
       <c r="P7" t="n">
-        <v>333.5997130128019</v>
+        <v>333.739962152181</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39121,28 +39219,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4462139713396626</v>
+        <v>-0.4604967730226334</v>
       </c>
       <c r="J8" t="n">
+        <v>759</v>
+      </c>
+      <c r="K8" t="n">
         <v>757</v>
       </c>
-      <c r="K8" t="n">
-        <v>755</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.02749790315380751</v>
+        <v>0.02924893988103294</v>
       </c>
       <c r="M8" t="n">
-        <v>17.66819021764264</v>
+        <v>17.69762781888377</v>
       </c>
       <c r="N8" t="n">
-        <v>418.5396752938715</v>
+        <v>419.5806158994147</v>
       </c>
       <c r="O8" t="n">
-        <v>20.4582422337275</v>
+        <v>20.48366705205429</v>
       </c>
       <c r="P8" t="n">
-        <v>328.4566414810795</v>
+        <v>328.606557204657</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39199,28 +39297,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3961819313118646</v>
+        <v>-0.411329042419815</v>
       </c>
       <c r="J9" t="n">
+        <v>759</v>
+      </c>
+      <c r="K9" t="n">
         <v>757</v>
       </c>
-      <c r="K9" t="n">
-        <v>755</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01942281847200489</v>
+        <v>0.02091547156405038</v>
       </c>
       <c r="M9" t="n">
-        <v>18.72621114716035</v>
+        <v>18.75745874060638</v>
       </c>
       <c r="N9" t="n">
-        <v>470.9970610958311</v>
+        <v>472.1671473757028</v>
       </c>
       <c r="O9" t="n">
-        <v>21.70246670532709</v>
+        <v>21.72940743268676</v>
       </c>
       <c r="P9" t="n">
-        <v>327.0737854780817</v>
+        <v>327.2327731938095</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39277,28 +39375,28 @@
         <v>0.0471</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4160497586002321</v>
+        <v>-0.433944442762787</v>
       </c>
       <c r="J10" t="n">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="K10" t="n">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0146672801633132</v>
+        <v>0.01594661287967947</v>
       </c>
       <c r="M10" t="n">
-        <v>22.800437628039</v>
+        <v>22.83653720948642</v>
       </c>
       <c r="N10" t="n">
-        <v>702.5203980863041</v>
+        <v>704.0998223758386</v>
       </c>
       <c r="O10" t="n">
-        <v>26.50510135966856</v>
+        <v>26.53487935483858</v>
       </c>
       <c r="P10" t="n">
-        <v>327.6416222661748</v>
+        <v>327.827754381325</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39336,7 +39434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K758"/>
+  <dimension ref="A1:K760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82465,6 +82563,120 @@
         </is>
       </c>
     </row>
+    <row r="759">
+      <c r="A759" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:40+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>-43.04852660619882,173.07193729047836</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>-43.04825372899743,173.07109673912328</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>-43.04792599114258,173.07023664071986</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>-43.04793916115373,173.06925413837365</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>-43.04782138908654,173.06831305434568</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>-43.04803179351888,173.06737767476585</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>-43.04802768466134,173.06645415611004</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>-43.048042230146834,173.06555577619514</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>-43.04802358466592,173.06465524319322</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>-43.048531457866844,173.07193593305433</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>-43.04826334410887,173.07109404888095</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>-43.04792599114258,173.07023664071986</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>-43.04795746424243,173.0692519989365</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>-43.047845961471204,173.0683120382732</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>-43.048045840331554,173.0673779038956</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>-43.04803604985158,173.06645469900283</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>-43.048051494823135,173.06555637737262</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>-43.04802790218652,173.06465552331093</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
